--- a/4_outputs/final/Table31.xlsx
+++ b/4_outputs/final/Table31.xlsx
@@ -422,13 +422,13 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.42 (1,689)</t>
+          <t>0.415 (1,689)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.44 (357)</t>
+          <t>0.443 (357)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.42 (1,191)</t>
+          <t>0.415 (1,191)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.56 (141)</t>
+          <t>0.556 (141)</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.30 (1,508)</t>
+          <t>0.299 (1,508)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.35 (240)</t>
+          <t>0.345 (240)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.29 (1,196)</t>
+          <t>0.294 (1,196)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.45 (72)</t>
+          <t>0.454 (72)</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.49 (2,408)</t>
+          <t>0.495 (2,408)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.36 (643)</t>
+          <t>0.362 (643)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.55 (1,707)</t>
+          <t>0.554 (1,707)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.70 (58)</t>
+          <t>0.695 (58)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.27 (2,055)</t>
+          <t>0.267 (2,055)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.21 (274)</t>
+          <t>0.205 (274)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.29 (1,718)</t>
+          <t>0.287 (1,718)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.40 (63)</t>
+          <t>0.395 (63)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.28 (2,005)</t>
+          <t>0.278 (2,005)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.28 (272)</t>
+          <t>0.276 (272)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.28 (1,531)</t>
+          <t>0.282 (1,531)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.41 (202)</t>
+          <t>0.411 (202)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.29 (1,206)</t>
+          <t>0.292 (1,206)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.35 (137)</t>
+          <t>0.346 (137)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.29 (1,038)</t>
+          <t>0.292 (1,038)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.42 (31)</t>
+          <t>0.422 (31)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.43 (1,578)</t>
+          <t>0.427 (1,578)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.51 (358)</t>
+          <t>0.511 (358)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.41 (1,147)</t>
+          <t>0.409 (1,147)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.59 (73)</t>
+          <t>0.591 (73)</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.39 (1,886)</t>
+          <t>0.387 (1,886)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.40 (309)</t>
+          <t>0.395 (309)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.40 (1,558)</t>
+          <t>0.397 (1,558)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.54 (19)</t>
+          <t>0.536 (19)</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.31 (2,986)</t>
+          <t>0.315 (2,986)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.27 (1,838)</t>
+          <t>0.272 (1,838)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.54 (1,116)</t>
+          <t>0.545 (1,116)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.46 (32)</t>
+          <t>0.459 (32)</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.27 (1,085)</t>
+          <t>0.272 (1,085)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.33 (258)</t>
+          <t>0.331 (258)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.28 (774)</t>
+          <t>0.278 (774)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.40 (53)</t>
+          <t>0.402 (53)</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.45 (1,658)</t>
+          <t>0.449 (1,658)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.43 (175)</t>
+          <t>0.428 (175)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.46 (1,474)</t>
+          <t>0.456 (1,474)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.57 (9)</t>
+          <t>0.573 (9)</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.30 (1,132)</t>
+          <t>0.296 (1,132)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.38 (178)</t>
+          <t>0.384 (178)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.30 (947)</t>
+          <t>0.297 (947)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.49 (7)</t>
+          <t>0.488 (7)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.48 (3,084)</t>
+          <t>0.480 (3,084)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.44 (613)</t>
+          <t>0.437 (613)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.44 (1,268)</t>
+          <t>0.444 (1,268)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.58 (1,203)</t>
+          <t>0.576 (1,203)</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.36 (1,293)</t>
+          <t>0.360 (1,293)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.37 (216)</t>
+          <t>0.372 (216)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.35 (856)</t>
+          <t>0.354 (856)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.49 (221)</t>
+          <t>0.487 (221)</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.24 (1,484)</t>
+          <t>0.238 (1,484)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.29 (299)</t>
+          <t>0.289 (299)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.24 (1,108)</t>
+          <t>0.237 (1,108)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.41 (77)</t>
+          <t>0.409 (77)</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.33 (4,890)</t>
+          <t>0.329 (4,890)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.20 (1,092)</t>
+          <t>0.195 (1,092)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.38 (1,395)</t>
+          <t>0.377 (1,395)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.51 (2,403)</t>
+          <t>0.506 (2,403)</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.18 (3,645)</t>
+          <t>0.177 (3,645)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.18 (859)</t>
+          <t>0.181 (859)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.16 (1,322)</t>
+          <t>0.165 (1,322)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.26 (1,464)</t>
+          <t>0.260 (1,464)</t>
         </is>
       </c>
     </row>
@@ -1312,42 +1312,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.613</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.914</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.453</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.966</t>
         </is>
       </c>
     </row>
